--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.30443623076555</v>
+        <v>8.011970887499404</v>
       </c>
       <c r="D2" t="n">
-        <v>46.7497637166495</v>
+        <v>7.596836603955545</v>
       </c>
       <c r="E2" t="n">
-        <v>9.434795422896579</v>
+        <v>1.533154256220694</v>
       </c>
       <c r="F2" t="n">
-        <v>14.21319402192934</v>
+        <v>2.309644028563517</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.85651494705356</v>
+        <v>9.239183678896204</v>
       </c>
       <c r="D3" t="n">
-        <v>56.09587450017325</v>
+        <v>9.115579606278153</v>
       </c>
       <c r="E3" t="n">
-        <v>9.434795422896579</v>
+        <v>1.533154256220694</v>
       </c>
       <c r="F3" t="n">
-        <v>14.21319402192934</v>
+        <v>2.309644028563517</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.07235618088441</v>
+        <v>5.374257879393717</v>
       </c>
       <c r="D4" t="n">
-        <v>35.44496260710783</v>
+        <v>5.759806423655021</v>
       </c>
       <c r="E4" t="n">
-        <v>9.434795422896579</v>
+        <v>1.533154256220694</v>
       </c>
       <c r="F4" t="n">
-        <v>14.21319402192934</v>
+        <v>2.309644028563517</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.28722323060618</v>
+        <v>9.796673774973504</v>
       </c>
       <c r="D5" t="n">
-        <v>17.47570572416364</v>
+        <v>2.839802180176592</v>
       </c>
       <c r="E5" t="n">
-        <v>9.434795422896579</v>
+        <v>1.533154256220694</v>
       </c>
       <c r="F5" t="n">
-        <v>14.21319402192934</v>
+        <v>2.309644028563517</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.44591782176526</v>
+        <v>8.522461646036854</v>
       </c>
       <c r="D6" t="n">
-        <v>23.86565306850004</v>
+        <v>3.878168623631256</v>
       </c>
       <c r="E6" t="n">
-        <v>9.434795422896579</v>
+        <v>1.533154256220694</v>
       </c>
       <c r="F6" t="n">
-        <v>14.21319402192934</v>
+        <v>2.309644028563517</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
